--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,6 +1094,136 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123300867</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björnåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600575</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6872358</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Pattranit Kwanruen, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91243</v>
+        <v>91242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91253</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91253</v>
+        <v>91270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>123300867</v>
       </c>
       <c r="B5" t="n">
-        <v>91275</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Pattranit Kwanruen, Douglas Skarp</t>
+          <t>Douglas Skarp, Pattranit Kwanruen, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp, Pattranit Kwanruen, Alexander Hoffmann</t>
+          <t>Alexander Hoffmann, Pattranit Kwanruen, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67351033</v>
+        <v>123300867</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnåsen, sydsluttning, Hls</t>
+          <t>Björnåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600684.1441960735</v>
+        <v>600575</v>
       </c>
       <c r="R2" t="n">
-        <v>6872383.979681734</v>
+        <v>6872358</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,24 +747,29 @@
           <t>Bergsjö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,49 +778,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Alexander Hoffmann, Pattranit Kwanruen, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80433829</v>
+        <v>67351033</v>
       </c>
       <c r="B3" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,40 +811,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4189</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan Björnåsen och Gammelbodtjärnarna, Hls</t>
+          <t>Björnåsen, sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600309.0824155962</v>
+        <v>600684</v>
       </c>
       <c r="R3" t="n">
-        <v>6872302.788565489</v>
+        <v>6872384</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på myrstack.</t>
+          <t>2017-08-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,29 +885,19 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tall och gran dominerar, skuggigt.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>stackmyror</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Formica (Formica)</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Myrstack # Formica (Formica)</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,12 +918,7 @@
         <v>80171836</v>
       </c>
       <c r="B4" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600309.0824155962</v>
+        <v>600309</v>
       </c>
       <c r="R4" t="n">
-        <v>6872302.788565489</v>
+        <v>6872303</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1027,19 +986,9 @@
           <t>2019-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,62 +1045,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300867</v>
+        <v>80433829</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnåsen, Hls</t>
+          <t>Mellan Björnåsen och Gammelbodtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600575</v>
+        <v>600309</v>
       </c>
       <c r="R5" t="n">
-        <v>6872358</v>
+        <v>6872303</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1173,29 +1111,19 @@
           <t>Bergsjö</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:22</t>
+          <t>2019-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:22</t>
+          <t>2019-10-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på myrstack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,21 +1132,168 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tall och gran dominerar, skuggigt.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>stackmyror</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Formica (Formica)</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Myrstack # Formica (Formica)</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Myhrer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123300866</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600611</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6872434</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Alexander Hoffmann, Pattranit Kwanruen, Douglas Skarp</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 31054-2024 artfynd.xlsx
+++ b/artfynd/A 31054-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123300867</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67351033</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80171836</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,6 +1193,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80433829</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,8 +1323,20 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123300866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>